--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F03311-2739-495A-9430-6C1B4CCF37C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101AD084-ABFC-4B27-B7DF-0C35F0518A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -68,6 +68,21 @@
     </rPh>
     <rPh sb="11" eb="13">
       <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライトを入手
+F or Hキーでライト点滅</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暗すぎてよく見えない…</t>
+    <rPh sb="0" eb="1">
+      <t>クラ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ミ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -440,16 +455,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="37.5">
       <c r="A6">
         <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">

--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101AD084-ABFC-4B27-B7DF-0C35F0518A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3434B4F7-E6AC-462C-A6F2-4041D3C43283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -84,6 +84,39 @@
     <rPh sb="6" eb="7">
       <t>ミ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeJapanese</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageEnglish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeEnglish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Inventory is full.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>You cannot carry any more of this item.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cannot use while stamina boost is active.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Obtained Flashlight.
+Press F or H to toggle light.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>It's too dark to see…</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -412,86 +445,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="37.125" customWidth="1"/>
+    <col min="3" max="3" width="21.875" customWidth="1"/>
+    <col min="4" max="4" width="36.375" customWidth="1"/>
+    <col min="5" max="5" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="37.5">
+      <c r="C5">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3434B4F7-E6AC-462C-A6F2-4041D3C43283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3055B3A-9E5B-4609-8F8A-0903A730A6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -117,6 +117,13 @@
   </si>
   <si>
     <t>It's too dark to see…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>使用していない</t>
+    <rPh sb="0" eb="2">
+      <t>シヨウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -445,16 +452,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="37.125" customWidth="1"/>
     <col min="3" max="3" width="21.875" customWidth="1"/>
     <col min="4" max="4" width="36.375" customWidth="1"/>
     <col min="5" max="5" width="18.125" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -471,12 +479,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -493,7 +501,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -510,7 +518,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -526,8 +534,11 @@
       <c r="E5">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="37.5">
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -544,7 +555,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -561,27 +572,27 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3055B3A-9E5B-4609-8F8A-0903A730A6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6715A1CB-B046-4848-8FF9-E7BB596BAE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,23 +45,6 @@
     <t>message</t>
   </si>
   <si>
-    <t>手持ちのアイテムがいっぱいです</t>
-    <rPh sb="0" eb="2">
-      <t>テモ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>このアイテムはこれ以上持てません</t>
-    <rPh sb="9" eb="11">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>モ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>スタミナ増強中のため、使用できません。</t>
     <rPh sb="4" eb="7">
       <t>ゾウキョウチュウ</t>
@@ -72,21 +55,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ライトを入手
-F or Hキーでライト点滅</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>暗すぎてよく見えない…</t>
-    <rPh sb="0" eb="1">
-      <t>クラ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>messageSizeJapanese</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -123,6 +91,32 @@
     <t>使用していない</t>
     <rPh sb="0" eb="2">
       <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="ても"&gt;手持&lt;/r&gt;ちのアイテムがいっぱいだ…</t>
+    <rPh sb="8" eb="10">
+      <t>テモチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このアイテムはこれ&lt;r="いじょう"&gt;以上&lt;/r&gt;&lt;r="も"&gt;持&lt;/r&gt;てない…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライトを&lt;r="にゅうしゅ"&gt;入手&lt;/r&gt; 
+F or Hキーでライト&lt;r="てんめつ"&gt;点滅&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="くら"&gt;暗&lt;/r&gt;すぎてよく&lt;r="み"&gt;見&lt;/r&gt;えない…</t>
+    <rPh sb="8" eb="9">
+      <t>アン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ケン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -455,7 +449,7 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="37.125" customWidth="1"/>
+    <col min="2" max="2" width="37.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="21.875" customWidth="1"/>
     <col min="4" max="4" width="36.375" customWidth="1"/>
     <col min="5" max="5" width="18.125" customWidth="1"/>
@@ -466,17 +460,17 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -484,35 +478,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>2</v>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C3">
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="37.5">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C4">
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>22</v>
@@ -522,51 +516,51 @@
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
+      <c r="B5" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="C5">
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="37.5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="56.25">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" ht="37.5">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>22</v>

--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6715A1CB-B046-4848-8FF9-E7BB596BAE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8218A00-E6B3-414B-BE04-F793A620EAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -120,12 +120,36 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>随身携带的物品已经满了…</t>
+  </si>
+  <si>
+    <t>这个物品无法再持有更多了…</t>
+  </si>
+  <si>
+    <t>由于耐力增强中，无法使用。</t>
+  </si>
+  <si>
+    <t>获得了手电筒
+按 F 或 H 键开关灯光</t>
+  </si>
+  <si>
+    <t>太黑了看不清楚…</t>
+  </si>
+  <si>
+    <t>messageChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +163,12 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -161,11 +191,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -446,17 +480,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="37.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="21.875" customWidth="1"/>
     <col min="4" max="4" width="36.375" customWidth="1"/>
     <col min="5" max="5" width="18.125" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
+    <col min="6" max="6" width="26.5" customWidth="1"/>
+    <col min="7" max="7" width="22.125" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -472,13 +508,19 @@
       <c r="E1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="37.5">
+    <row r="3" spans="1:8" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -494,8 +536,14 @@
       <c r="E3">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="37.5">
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="37.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -511,8 +559,14 @@
       <c r="E4">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="37.5">
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -528,11 +582,17 @@
       <c r="E5">
         <v>22</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="3">
+        <v>22</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="56.25">
+    <row r="6" spans="1:8" ht="56.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -548,8 +608,14 @@
       <c r="E6">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="37.5">
+      <c r="F6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="37.5">
       <c r="A7">
         <v>5</v>
       </c>
@@ -565,28 +631,34 @@
       <c r="E7">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8218A00-E6B3-414B-BE04-F793A620EAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1E056E-830C-4FD0-B8B4-7E9B7F6161A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -144,12 +144,33 @@
     <t>messageSizeChinese01</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>隨身攜帶的物品已經滿了…</t>
+  </si>
+  <si>
+    <t>這個物品無法再持有更多了…</t>
+  </si>
+  <si>
+    <t>由於耐力增強中，無法使用。</t>
+  </si>
+  <si>
+    <t>獲得了手電筒
+按 F 或 H 鍵開關燈光</t>
+  </si>
+  <si>
+    <t>messageChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,6 +190,12 @@
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -191,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -200,6 +227,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -480,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="37.125" style="1" customWidth="1"/>
@@ -488,11 +520,11 @@
     <col min="4" max="4" width="36.375" customWidth="1"/>
     <col min="5" max="5" width="18.125" customWidth="1"/>
     <col min="6" max="6" width="26.5" customWidth="1"/>
-    <col min="7" max="7" width="22.125" customWidth="1"/>
-    <col min="8" max="8" width="9" style="1"/>
+    <col min="7" max="9" width="22.125" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -514,13 +546,21 @@
       <c r="G1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="H1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="37.5">
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:10" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -542,8 +582,14 @@
       <c r="G3" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="37.5">
+      <c r="H3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="37.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -565,8 +611,14 @@
       <c r="G4" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="37.5">
+      <c r="H4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -588,11 +640,17 @@
       <c r="G5" s="3">
         <v>22</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="6">
+        <v>22</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="56.25">
+    <row r="6" spans="1:10" ht="56.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -614,8 +672,14 @@
       <c r="G6" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="37.5">
+      <c r="H6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="37.5">
       <c r="A7">
         <v>5</v>
       </c>
@@ -637,28 +701,34 @@
       <c r="G7" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1E056E-830C-4FD0-B8B4-7E9B7F6161A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE481B7-3A97-42B9-A0AE-AAA3EEDF905D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -164,6 +164,28 @@
   <si>
     <t>messageSizeChinese02</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSpanish</t>
+  </si>
+  <si>
+    <t>messageSizeSpanish</t>
+  </si>
+  <si>
+    <t>El inventario está lleno...</t>
+  </si>
+  <si>
+    <t>No puedes llevar más de este objeto...</t>
+  </si>
+  <si>
+    <t>No se puede usar mientras el aumento de resistencia está activo.</t>
+  </si>
+  <si>
+    <t>Has obtenido una linterna.
+Pulsa F o H para encenderla o apagarla.</t>
+  </si>
+  <si>
+    <t>Está demasiado oscuro para ver bien...</t>
   </si>
 </sst>
 </file>
@@ -218,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -227,11 +249,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -512,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="37.125" style="1" customWidth="1"/>
@@ -520,11 +545,11 @@
     <col min="4" max="4" width="36.375" customWidth="1"/>
     <col min="5" max="5" width="18.125" customWidth="1"/>
     <col min="6" max="6" width="26.5" customWidth="1"/>
-    <col min="7" max="9" width="22.125" customWidth="1"/>
-    <col min="10" max="10" width="9" style="1"/>
+    <col min="7" max="11" width="22.125" customWidth="1"/>
+    <col min="12" max="12" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -546,21 +571,27 @@
       <c r="G1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="J1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" spans="1:10" ht="37.5">
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="1:12" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -582,14 +613,20 @@
       <c r="G3" s="3">
         <v>22</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="37.5">
+      <c r="I3" s="5">
+        <v>22</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="37.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -611,14 +648,20 @@
       <c r="G4" s="3">
         <v>22</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="37.5">
+      <c r="I4" s="5">
+        <v>22</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -640,17 +683,23 @@
       <c r="G5" s="3">
         <v>22</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="6">
-        <v>22</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="I5" s="5">
+        <v>22</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="6">
+        <v>22</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="56.25">
+    <row r="6" spans="1:12" ht="75">
       <c r="A6">
         <v>4</v>
       </c>
@@ -672,14 +721,20 @@
       <c r="G6" s="3">
         <v>22</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="37.5">
+      <c r="I6" s="5">
+        <v>22</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="37.5">
       <c r="A7">
         <v>5</v>
       </c>
@@ -701,34 +756,40 @@
       <c r="G7" s="3">
         <v>22</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="I7" s="5">
+        <v>22</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE481B7-3A97-42B9-A0AE-AAA3EEDF905D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6C4526-910D-453F-81ED-34FF75CD2BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -186,6 +186,28 @@
   </si>
   <si>
     <t>Está demasiado oscuro para ver bien...</t>
+  </si>
+  <si>
+    <t>messagePortuguese</t>
+  </si>
+  <si>
+    <t>messageSizePortuguese</t>
+  </si>
+  <si>
+    <t>O inventário está cheio...</t>
+  </si>
+  <si>
+    <t>Você não pode carregar mais deste item...</t>
+  </si>
+  <si>
+    <t>Não é possível usar enquanto o aumento de resistência estiver ativo.</t>
+  </si>
+  <si>
+    <t>Lanterna obtida.
+Pressione F ou H para ligar/desligar a luz.</t>
+  </si>
+  <si>
+    <t>Está escuro demais para ver bem...</t>
   </si>
 </sst>
 </file>
@@ -537,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="37.125" style="1" customWidth="1"/>
@@ -545,11 +567,11 @@
     <col min="4" max="4" width="36.375" customWidth="1"/>
     <col min="5" max="5" width="18.125" customWidth="1"/>
     <col min="6" max="6" width="26.5" customWidth="1"/>
-    <col min="7" max="11" width="22.125" customWidth="1"/>
-    <col min="12" max="12" width="9" style="1"/>
+    <col min="7" max="13" width="22.125" customWidth="1"/>
+    <col min="14" max="14" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -577,21 +599,27 @@
       <c r="I1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="L1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" ht="37.5">
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -619,14 +647,20 @@
       <c r="I3" s="5">
         <v>22</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="37.5">
+      <c r="K3">
+        <v>22</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="37.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -654,14 +688,20 @@
       <c r="I4" s="5">
         <v>22</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="37.5">
+      <c r="K4">
+        <v>22</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -689,17 +729,23 @@
       <c r="I5" s="5">
         <v>22</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="6">
-        <v>22</v>
-      </c>
-      <c r="L5" s="1" t="s">
+      <c r="K5">
+        <v>22</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="6">
+        <v>22</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="75">
+    <row r="6" spans="1:14" ht="75">
       <c r="A6">
         <v>4</v>
       </c>
@@ -727,14 +773,20 @@
       <c r="I6" s="5">
         <v>22</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K6" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="37.5">
+      <c r="K6">
+        <v>22</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="37.5">
       <c r="A7">
         <v>5</v>
       </c>
@@ -762,34 +814,40 @@
       <c r="I7" s="5">
         <v>22</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="K7">
+        <v>22</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6C4526-910D-453F-81ED-34FF75CD2BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DE4677-2FD9-4CB3-9768-1BE38C7A1658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -208,6 +208,43 @@
   </si>
   <si>
     <t>Está escuro demais para ver bem...</t>
+  </si>
+  <si>
+    <t>&lt;r="ほうそう"&gt;放送のスイッチをオフにした</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Turned off the broadcast switch.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>关掉了广播开关</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>關掉了廣播開關</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Apagué el interruptor de la transmisión.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Desliguei o interruptor da transmissão.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>放送関連(インベントリ関係ない…)</t>
+    <rPh sb="0" eb="2">
+      <t>ホウソウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンレン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -262,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -275,10 +312,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -605,10 +638,10 @@
       <c r="K1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -616,8 +649,6 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
     </row>
     <row r="3" spans="1:14" ht="37.5">
       <c r="A3">
@@ -653,10 +684,10 @@
       <c r="K3">
         <v>22</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3">
         <v>22</v>
       </c>
     </row>
@@ -694,10 +725,10 @@
       <c r="K4">
         <v>22</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" t="s">
         <v>39</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4">
         <v>22</v>
       </c>
     </row>
@@ -735,10 +766,10 @@
       <c r="K5">
         <v>22</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5">
         <v>22</v>
       </c>
       <c r="N5" s="1" t="s">
@@ -779,10 +810,10 @@
       <c r="K6">
         <v>22</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6">
         <v>22</v>
       </c>
     </row>
@@ -820,16 +851,55 @@
       <c r="K7">
         <v>22</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" t="s">
         <v>42</v>
       </c>
-      <c r="M7" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="M7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="75">
       <c r="A8">
         <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="1">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="2">
+        <v>22</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="2">
+        <v>22</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="2">
+        <v>18</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" s="2">
+        <v>18</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:14">

--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DE4677-2FD9-4CB3-9768-1BE38C7A1658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EF7ECD-712B-4BEC-A265-C21DF38D4377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -210,10 +210,6 @@
     <t>Está escuro demais para ver bem...</t>
   </si>
   <si>
-    <t>&lt;r="ほうそう"&gt;放送のスイッチをオフにした</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Turned off the broadcast switch.</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -244,6 +240,10 @@
     <rPh sb="11" eb="13">
       <t>カンケイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="ほうそう"&gt;放送&lt;/r&gt;のスイッチをオフにした</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -863,43 +863,43 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="1">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="1">
-        <v>22</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="1">
-        <v>22</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2">
+        <v>22</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="2">
-        <v>22</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="2">
+        <v>22</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="I8" s="2">
-        <v>22</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="K8" s="2">
         <v>18</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M8" s="2">
         <v>18</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:14">

--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EF7ECD-712B-4BEC-A265-C21DF38D4377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065A8E9B-2297-47F1-B6E3-733103A08A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -244,6 +244,41 @@
   </si>
   <si>
     <t>&lt;r="ほうそう"&gt;放送&lt;/r&gt;のスイッチをオフにした</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シャッターを&lt;r="あ"&gt;開&lt;/r&gt;けた</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シャッター関連(インベントリ関係ない…)</t>
+    <rPh sb="5" eb="7">
+      <t>カンレン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Opened the shutter.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>打开了卷帘门</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>打開了捲簾門</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Abrí la contraventana.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Abri a veneziana.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -902,9 +937,48 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" ht="93.75">
       <c r="A9">
         <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="1">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>22</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="1">
+        <v>22</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="1">
+        <v>22</v>
+      </c>
+      <c r="J9" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" s="1">
+        <v>22</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="1">
+        <v>22</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:14">
